--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120855818</v>
       </c>
       <c r="B2" t="n">
-        <v>79589</v>
+        <v>79592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,435 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122747441</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101608</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Asppraktbagge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecilonota variolosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Paykull, 1799)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenås SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>581595</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6514132</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122747435</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90848</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenås SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581462</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6514175</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122747437</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4867</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenås SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581564</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6514131</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122747438</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4867</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenås SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>581590</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6514155</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>122747435</v>
       </c>
       <c r="B4" t="n">
-        <v>90848</v>
+        <v>90951</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747437</v>
+        <v>122747438</v>
       </c>
       <c r="B5" t="n">
         <v>4867</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581564</v>
+        <v>581590</v>
       </c>
       <c r="R5" t="n">
-        <v>6514131</v>
+        <v>6514155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747438</v>
+        <v>122747437</v>
       </c>
       <c r="B6" t="n">
         <v>4867</v>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581590</v>
+        <v>581564</v>
       </c>
       <c r="R6" t="n">
-        <v>6514155</v>
+        <v>6514131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747441</v>
+        <v>122747435</v>
       </c>
       <c r="B3" t="n">
-        <v>5023</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101608</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581595</v>
+        <v>581462</v>
       </c>
       <c r="R3" t="n">
-        <v>6514132</v>
+        <v>6514175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747435</v>
+        <v>122747441</v>
       </c>
       <c r="B4" t="n">
-        <v>90951</v>
+        <v>5023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>101608</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581462</v>
+        <v>581595</v>
       </c>
       <c r="R4" t="n">
-        <v>6514175</v>
+        <v>6514132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747438</v>
+        <v>122747437</v>
       </c>
       <c r="B5" t="n">
         <v>4867</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581590</v>
+        <v>581564</v>
       </c>
       <c r="R5" t="n">
-        <v>6514155</v>
+        <v>6514131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747437</v>
+        <v>122747438</v>
       </c>
       <c r="B6" t="n">
         <v>4867</v>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581564</v>
+        <v>581590</v>
       </c>
       <c r="R6" t="n">
-        <v>6514131</v>
+        <v>6514155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747435</v>
+        <v>122747441</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>5023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>101608</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581462</v>
+        <v>581595</v>
       </c>
       <c r="R3" t="n">
-        <v>6514175</v>
+        <v>6514132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747441</v>
+        <v>122747437</v>
       </c>
       <c r="B4" t="n">
-        <v>5023</v>
+        <v>4867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101608</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R4" t="n">
-        <v>6514132</v>
+        <v>6514131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747437</v>
+        <v>122747435</v>
       </c>
       <c r="B5" t="n">
-        <v>4867</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581564</v>
+        <v>581462</v>
       </c>
       <c r="R5" t="n">
-        <v>6514131</v>
+        <v>6514175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747437</v>
+        <v>122747435</v>
       </c>
       <c r="B4" t="n">
-        <v>4867</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581564</v>
+        <v>581462</v>
       </c>
       <c r="R4" t="n">
-        <v>6514131</v>
+        <v>6514175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747435</v>
+        <v>122747437</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>4867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581462</v>
+        <v>581564</v>
       </c>
       <c r="R5" t="n">
-        <v>6514175</v>
+        <v>6514131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747441</v>
+        <v>122747437</v>
       </c>
       <c r="B3" t="n">
-        <v>5023</v>
+        <v>4867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101608</v>
+        <v>101675</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R3" t="n">
-        <v>6514132</v>
+        <v>6514131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1009,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747437</v>
+        <v>122747441</v>
       </c>
       <c r="B5" t="n">
-        <v>4867</v>
+        <v>5023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>101608</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R5" t="n">
-        <v>6514131</v>
+        <v>6514132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1080,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747435</v>
+        <v>122747438</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>4867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581462</v>
+        <v>581590</v>
       </c>
       <c r="R4" t="n">
-        <v>6514175</v>
+        <v>6514155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747441</v>
+        <v>122747435</v>
       </c>
       <c r="B5" t="n">
-        <v>5023</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101608</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581595</v>
+        <v>581462</v>
       </c>
       <c r="R5" t="n">
-        <v>6514132</v>
+        <v>6514175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747438</v>
+        <v>122747441</v>
       </c>
       <c r="B6" t="n">
-        <v>4867</v>
+        <v>5023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101675</v>
+        <v>101608</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581590</v>
+        <v>581595</v>
       </c>
       <c r="R6" t="n">
-        <v>6514155</v>
+        <v>6514132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,6 +1186,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747437</v>
+        <v>122747441</v>
       </c>
       <c r="B3" t="n">
-        <v>4867</v>
+        <v>5023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101675</v>
+        <v>101608</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R3" t="n">
-        <v>6514131</v>
+        <v>6514132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1004,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747435</v>
+        <v>122747437</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>4867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581462</v>
+        <v>581564</v>
       </c>
       <c r="R5" t="n">
-        <v>6514175</v>
+        <v>6514131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747441</v>
+        <v>122747435</v>
       </c>
       <c r="B6" t="n">
-        <v>5023</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101608</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581595</v>
+        <v>581462</v>
       </c>
       <c r="R6" t="n">
-        <v>6514132</v>
+        <v>6514175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747441</v>
+        <v>122747437</v>
       </c>
       <c r="B3" t="n">
-        <v>5023</v>
+        <v>4867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101608</v>
+        <v>101675</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R3" t="n">
-        <v>6514132</v>
+        <v>6514131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747438</v>
+        <v>122747441</v>
       </c>
       <c r="B4" t="n">
-        <v>4867</v>
+        <v>5023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>101608</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581590</v>
+        <v>581595</v>
       </c>
       <c r="R4" t="n">
-        <v>6514155</v>
+        <v>6514132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747437</v>
+        <v>122747435</v>
       </c>
       <c r="B5" t="n">
-        <v>4867</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581564</v>
+        <v>581462</v>
       </c>
       <c r="R5" t="n">
-        <v>6514131</v>
+        <v>6514175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747435</v>
+        <v>122747438</v>
       </c>
       <c r="B6" t="n">
-        <v>90963</v>
+        <v>4867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>101675</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581462</v>
+        <v>581590</v>
       </c>
       <c r="R6" t="n">
-        <v>6514175</v>
+        <v>6514155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747437</v>
+        <v>122747435</v>
       </c>
       <c r="B3" t="n">
-        <v>4867</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581564</v>
+        <v>581462</v>
       </c>
       <c r="R3" t="n">
-        <v>6514131</v>
+        <v>6514175</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747441</v>
+        <v>122747438</v>
       </c>
       <c r="B4" t="n">
-        <v>5023</v>
+        <v>4867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101608</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581595</v>
+        <v>581590</v>
       </c>
       <c r="R4" t="n">
-        <v>6514132</v>
+        <v>6514155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,11 +974,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747435</v>
+        <v>122747441</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>5023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>101608</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581462</v>
+        <v>581595</v>
       </c>
       <c r="R5" t="n">
-        <v>6514175</v>
+        <v>6514132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1080,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747438</v>
+        <v>122747437</v>
       </c>
       <c r="B6" t="n">
         <v>4867</v>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581590</v>
+        <v>581564</v>
       </c>
       <c r="R6" t="n">
-        <v>6514155</v>
+        <v>6514131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747435</v>
+        <v>122747438</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>4867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>101675</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581462</v>
+        <v>581590</v>
       </c>
       <c r="R3" t="n">
-        <v>6514175</v>
+        <v>6514155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747438</v>
+        <v>122747435</v>
       </c>
       <c r="B4" t="n">
-        <v>4867</v>
+        <v>90966</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581590</v>
+        <v>581462</v>
       </c>
       <c r="R4" t="n">
-        <v>6514155</v>
+        <v>6514175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747441</v>
+        <v>122747437</v>
       </c>
       <c r="B5" t="n">
-        <v>5023</v>
+        <v>4867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101608</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R5" t="n">
-        <v>6514132</v>
+        <v>6514131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747437</v>
+        <v>122747441</v>
       </c>
       <c r="B6" t="n">
-        <v>4867</v>
+        <v>5023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1122,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101675</v>
+        <v>101608</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Asppraktbagge</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Poecilonota variolosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Paykull, 1799)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581564</v>
+        <v>581595</v>
       </c>
       <c r="R6" t="n">
-        <v>6514131</v>
+        <v>6514132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,6 +1186,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747435</v>
+        <v>122747437</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>4867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581462</v>
+        <v>581564</v>
       </c>
       <c r="R4" t="n">
-        <v>6514175</v>
+        <v>6514131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747437</v>
+        <v>122747435</v>
       </c>
       <c r="B5" t="n">
-        <v>4867</v>
+        <v>90968</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581564</v>
+        <v>581462</v>
       </c>
       <c r="R5" t="n">
-        <v>6514131</v>
+        <v>6514175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120855818</v>
       </c>
       <c r="B2" t="n">
-        <v>80259</v>
+        <v>80260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120855818</v>
       </c>
       <c r="B2" t="n">
-        <v>80260</v>
+        <v>80261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120855818</v>
       </c>
       <c r="B2" t="n">
-        <v>80261</v>
+        <v>80263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120855818</v>
       </c>
       <c r="B2" t="n">
-        <v>80263</v>
+        <v>80264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120855818</v>
       </c>
       <c r="B2" t="n">
-        <v>80264</v>
+        <v>80265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120855818</v>
+        <v>95348439</v>
       </c>
       <c r="B2" t="n">
-        <v>80265</v>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,57 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2080</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mogetorp, Mogetorp, Srm</t>
+          <t>Havregölet, Skogsklocka 200 m n vid bäcken, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581593</v>
+        <v>581064</v>
       </c>
       <c r="R2" t="n">
-        <v>6514137</v>
+        <v>6514101</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,29 +758,19 @@
           <t>Kila</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>D-Nyk-0546</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal solbelyst asp i vägkant. Även spår av asppraktbagge i basen. Mikroskoperad och artbestämd av Fredrik Jonsson.</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,81 +779,96 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>bert lindgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747438</v>
+        <v>95348629</v>
       </c>
       <c r="B3" t="n">
-        <v>4867</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101675</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenås SV, Srm</t>
+          <t>Havregölet , skogsklocka 400 m nno, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581590</v>
+        <v>581297</v>
       </c>
       <c r="R3" t="n">
-        <v>6514155</v>
+        <v>6514202</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,14 +890,19 @@
           <t>Kila</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D-Nyk-0547</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +911,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>bert lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747437</v>
+        <v>122747435</v>
       </c>
       <c r="B4" t="n">
-        <v>4867</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +950,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581564</v>
+        <v>581462</v>
       </c>
       <c r="R4" t="n">
-        <v>6514131</v>
+        <v>6514175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,56 +1034,54 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747435</v>
+        <v>120855818</v>
       </c>
       <c r="B5" t="n">
-        <v>90968</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>2080</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenås SV, Srm</t>
+          <t>Mogetorp, Mogetorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581462</v>
+        <v>581593</v>
       </c>
       <c r="R5" t="n">
-        <v>6514175</v>
+        <v>6514137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,24 +1111,49 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal solbelyst asp i vägkant. Även spår av asppraktbagge i basen. Mikroskoperad och artbestämd av Fredrik Jonsson.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1110,45 +1161,36 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747441</v>
+        <v>122747437</v>
       </c>
       <c r="B6" t="n">
-        <v>5023</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101608</v>
+        <v>101675</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581595</v>
+        <v>581564</v>
       </c>
       <c r="R6" t="n">
-        <v>6514132</v>
+        <v>6514131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,11 +1238,6 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1223,7 +1260,108 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122747438</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenås SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>581590</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6514155</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 1509-2023 artfynd.xlsx
+++ b/artfynd/A 1509-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95348439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95348629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747435</t>
         </is>
       </c>
     </row>
@@ -1162,6 +1182,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120855818</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747437</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,8 +1394,21 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747438</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>